--- a/resources/school/school_talent.xlsx
+++ b/resources/school/school_talent.xlsx
@@ -1782,9 +1782,34 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
+      <c r="A16" s="16" t="n">
+        <v>103303</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>伤害提升20%</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Icon_120_shentong_1.png</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="26" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="23" t="n"/>
@@ -1932,7 +1957,7 @@
       <c r="A5" s="16" t="n">
         <v>101101</v>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>忽略目标10%攻击</t>
         </is>
@@ -1951,7 +1976,7 @@
       <c r="A6" s="16" t="n">
         <v>101102</v>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>忽略目标20%攻击</t>
         </is>
@@ -1970,7 +1995,7 @@
       <c r="A7" s="16" t="n">
         <v>101201</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>伤害提升20%</t>
         </is>
@@ -1989,7 +2014,7 @@
       <c r="A8" s="16" t="n">
         <v>101202</v>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>伤害提升40%</t>
         </is>
@@ -2008,7 +2033,7 @@
       <c r="A9" s="16" t="n">
         <v>101301</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>阵法效果增加3%</t>
         </is>
@@ -2027,7 +2052,7 @@
       <c r="A10" s="16" t="n">
         <v>101302</v>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>阵法效果增加6%</t>
         </is>
@@ -2046,7 +2071,7 @@
       <c r="A11" s="16" t="n">
         <v>102101</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>忽略目标20%攻击</t>
         </is>
@@ -2065,7 +2090,7 @@
       <c r="A12" s="16" t="n">
         <v>102102</v>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>忽略目标30%攻击</t>
         </is>
@@ -2084,7 +2109,7 @@
       <c r="A13" s="16" t="n">
         <v>102201</v>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>伤害提升45%</t>
         </is>
@@ -2103,7 +2128,7 @@
       <c r="A14" s="16" t="n">
         <v>102202</v>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>伤害提升55%</t>
         </is>
@@ -2122,7 +2147,7 @@
       <c r="A15" s="16" t="n">
         <v>102301</v>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>阵法效果增加6%</t>
         </is>
@@ -2141,7 +2166,7 @@
       <c r="A16" s="16" t="n">
         <v>102302</v>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>阵法效果增加12%</t>
         </is>
@@ -2160,7 +2185,7 @@
       <c r="A17" s="16" t="n">
         <v>103101</v>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>伤害倍率增加20%</t>
         </is>
@@ -2179,7 +2204,7 @@
       <c r="A18" s="16" t="n">
         <v>103102</v>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>伤害倍率增加40%</t>
         </is>
@@ -2198,7 +2223,7 @@
       <c r="A19" s="16" t="n">
         <v>103201</v>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>伤害暴击增加5%</t>
         </is>
@@ -2217,7 +2242,7 @@
       <c r="A20" s="16" t="n">
         <v>103202</v>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>伤害暴击增加15%</t>
         </is>
@@ -2236,7 +2261,7 @@
       <c r="A21" s="16" t="n">
         <v>103301</v>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>增加500护盾</t>
         </is>
@@ -2255,7 +2280,7 @@
       <c r="A22" s="16" t="n">
         <v>103302</v>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>增加1000护盾</t>
         </is>
@@ -2271,10 +2296,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="n"/>
+      <c r="A23" s="16" t="n">
+        <v>103303</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>伤害提升20%</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>600003</v>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="n"/>
+      <c r="A24" s="16" t="n">
+        <v>103304</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>伤害提升40%</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>600003</v>
+      </c>
     </row>
     <row r="25" customFormat="1" s="9">
       <c r="B25" s="22" t="n"/>
